--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -611,6 +611,7 @@
         <is>
           <t>Saudi Arabia: Goal 10회
 Germany: 2경기 각 Goal 1회
+TOTS: Outside Box Goal 5회
 CONMEBOL Libertadores: 5경기 각 Goal 1회
 Frauen-Bundesliga: 2경기 각 Goal 1회</t>
         </is>
@@ -625,6 +626,7 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Midfielder: Assist 4회
+TOTS: 1경기 각 Through Ball Assist 1회
 Defender: Assist 4회</t>
         </is>
       </c>
@@ -637,9 +639,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상
-TOTS: Outside Box Goal 5회
-Clean Sheet 5
+          <t>Clean Sheet 5
 Clean Sheet 4</t>
         </is>
       </c>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 250 SP Expires in 17 hours 1,250 total 5 Objectives 88% 12%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 250 SP Expires in 15 hours 1,250 total 5 Objectives 88% 12%</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Season 7 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 300 SP Expires in 17 hours 1,050 total 3 of 5 Objectives 85% 15%</t>
+          <t>Season 7 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 300 SP Expires in 15 hours 1,050 total 3 of 5 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 50 SP Expires in 17 hours 150 total 2 Objectives 93% 7%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 50 SP Expires in 15 hours 150 total 2 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Clean Sheet, Outside Box Goal, Finesse Goal 등 Goal/Assist 외 특수 수행조건을 표시합니다. 특수조건 파싱이 애매하면 원문을 그대로 표시합니다.</t>
+          <t>Clean Sheet 등 Goal/Assist가 아닌 특수 수행조건을 표시합니다. Outside Box Goal, Through Ball Assist처럼 골/어시 계열은 Goals/Assists로 분류합니다.</t>
         </is>
       </c>
     </row>
@@ -15168,12 +15168,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TOTS: Outside Box Goal 5회</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>TOTS: Outside Box Goal 5회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -18173,12 +18173,12 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TOTS: Outside Box Goal 5회</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>TOTS: Outside Box Goal 5회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -21285,6 +21285,7 @@
         <is>
           <t>Saudi Arabia: Goal 10회
 Germany: 2경기 각 Goal 1회
+TOTS: Outside Box Goal 5회
 CONMEBOL Libertadores: 5경기 각 Goal 1회
 Frauen-Bundesliga: 2경기 각 Goal 1회</t>
         </is>
@@ -21292,14 +21293,13 @@
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Midfielder: Assist 4회
+TOTS: 1경기 각 Through Ball Assist 1회
 Defender: Assist 4회</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상
-TOTS: Outside Box Goal 5회
-Clean Sheet 5
+          <t>Clean Sheet 5
 Clean Sheet 4</t>
         </is>
       </c>
@@ -21950,6 +21950,7 @@
         <is>
           <t>Saudi Arabia: Goal 10회
 Germany: 2경기 각 Goal 1회
+TOTS: Outside Box Goal 5회
 CONMEBOL Libertadores: 5경기 각 Goal 1회
 Frauen-Bundesliga: 2경기 각 Goal 1회</t>
         </is>
@@ -21957,14 +21958,13 @@
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Midfielder: Assist 4회
+TOTS: 1경기 각 Through Ball Assist 1회
 Defender: Assist 4회</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상
-TOTS: Outside Box Goal 5회
-Clean Sheet 5
+          <t>Clean Sheet 5
 Clean Sheet 4</t>
         </is>
       </c>
@@ -28265,12 +28265,12 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TOTS: Outside Box Goal 5회</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -28351,7 +28351,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>TOTS: Outside Box Goal 5회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -35624,6 +35624,7 @@
         <is>
           <t>Saudi Arabia: Goal 10회
 Germany: 2경기 각 Goal 1회
+TOTS: Outside Box Goal 5회
 CONMEBOL Libertadores: 5경기 각 Goal 1회
 Frauen-Bundesliga: 2경기 각 Goal 1회
 Any: 60경기 각 Goal 1회
@@ -35634,15 +35635,14 @@
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Midfielder: Assist 4회
+TOTS: 1경기 각 Through Ball Assist 1회
 Defender: Assist 4회
 Any: 35경기 각 Assist 1회</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각각 Through Ball Assist 1회 이상
-TOTS: Outside Box Goal 5회
-Clean Sheet 5
+          <t>Clean Sheet 5
 Clean Sheet 4
 Clean Sheet 15
 Clean Sheet 20

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -26,7 +26,7 @@
     <sheet name="How_To_Read" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$C$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SB_Action_Detail'!$A$1:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New_Report_Index'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action_Plan'!$A$1:$U$64</definedName>
@@ -530,12 +530,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -585,11 +585,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives (마감 5/12 02:00)
-Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives (마감 5/11 02:00)
-Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -601,137 +597,311 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Win 7
-Play 10</t>
+          <t>Win 7</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives (마감 5/12 02:00)
-Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives (마감 5/11 02:00)
-Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
+          <t>Evolution Revolution (마감 5/8 02:00)
+TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>필수 선발 요건</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bundesliga ≥1
-CONMEBOL Libertadores ≥1
-Germany ≥1
-ROSHN Saudi Pro League ≥1
-Saudi Arabia ≥2
-TOTS ≥1
-Uruguay ≥2</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives (마감 5/12 02:00)
-Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives (마감 5/11 02:00)
-Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>필수 선발 요건</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Bundesliga ≥1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Ilyas Ansah (마감 5/10 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>CONMEBOL Libertadores ≥1</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Germany ≥1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>ROSHN Saudi Pro League ≥1</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia ≥2</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TOTS ≥1</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Uruguay ≥2</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>교체로 투입해도 가능</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Midfielder
-Defender
-Frauen-Bundesliga</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives (마감 5/12 02:00)
-Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives (마감 5/11 02:00)
-Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Frauen-Bundesliga</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>To do (득점)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Saudi Arabia: Goal 10회
-Germany: 2경기 각 Goal 1회
-TOTS: Outside Box Goal 5회
-CONMEBOL Libertadores: 5경기 각 Goal 1회
-Frauen-Bundesliga: 2경기 각 Goal 1회</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives (마감 5/12 02:00)
-Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives (마감 5/11 02:00)
-Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia: Goal 10회</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Germany: 2경기 각 Goal 1회</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Ilyas Ansah (마감 5/10 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>TOTS: Outside Box Goal 5회</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CONMEBOL Libertadores: 5경기 각 Goal 1회</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Frauen-Bundesliga: 2경기 각 Goal 1회</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>To do (어시스트)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Midfielder: Assist 4회
-TOTS: 1경기 각 Through Ball Assist 1회
-Defender: Assist 4회</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives (마감 5/12 02:00)
-Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Midfielder: Assist 4회</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Defender: Assist 4회</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>To do (기타)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Clean Sheet 5
-Clean Sheet 4</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Evolution Revolution - EA SPORTS FC 26 Objectives (마감 5/9 02:00)
-TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives (마감 5/9 02:00)</t>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Clean Sheet 5</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Clean Sheet 4</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9"/>
+  <autoFilter ref="A1:C25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2172,17 +2342,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2255,17 +2425,17 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -2342,17 +2512,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2425,17 +2595,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -2508,17 +2678,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2591,17 +2761,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -2674,17 +2844,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -2757,17 +2927,17 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -2840,17 +3010,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2935,17 +3105,17 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -3026,17 +3196,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -3117,17 +3287,17 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -3212,17 +3382,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -3307,17 +3477,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -3394,17 +3564,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -3481,17 +3651,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -3572,17 +3742,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -3663,17 +3833,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -3750,17 +3920,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -3837,17 +4007,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -3924,17 +4094,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -4011,17 +4181,17 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -4098,17 +4268,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -4185,17 +4355,17 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -4276,17 +4446,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -4367,17 +4537,17 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -4458,17 +4628,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -4549,17 +4719,17 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -4636,17 +4806,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -4727,17 +4897,17 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -4818,17 +4988,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -4909,17 +5079,17 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -5000,17 +5170,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -5091,17 +5261,17 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -5182,17 +5352,17 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -5273,17 +5443,17 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -5629,17 +5799,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -5716,17 +5886,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -5803,17 +5973,17 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -5890,17 +6060,17 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -16810,7 +16980,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>A Few of my Favourite Things Complete the challenges below to earn some of the community's favourite players to Evolve! Nico O'Reilly Expires in 23 days 4 Objectives 60% 40%</t>
+          <t>A Few of my Favourite Things Complete the challenges below to earn some of the community's favourite players to Evolve! Nico O'Reilly Expires in 22 days 4 Objectives 60% 40%</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -16820,17 +16990,17 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -16847,7 +17017,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Musab Al-Juwair! Musab Al Juwair Expires in 5 days 100 total 5 Objectives 32% 68%</t>
+          <t>TOTS HM Musab Al-Juwair Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Musab Al-Juwair! Musab Al Juwair Expires in 4 days 100 total 5 Objectives 32% 68%</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -16857,17 +17027,17 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -16884,7 +17054,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Darwin Cup Compete in the Darwin Cup to earn SP, Evolutions, pack rewards and TOTS Honourable Mentions Serge Gnarbry and Glódís Perla Viggósdóttir! All rewards are untradeable. Evo Unlock Serge Gnabry Expires in 5 days 250 total 5 Objectives 83% 17%</t>
+          <t>Darwin Cup Compete in the Darwin Cup to earn SP, Evolutions, pack rewards and TOTS Honourable Mentions Serge Gnarbry and Glódís Perla Viggósdóttir! All rewards are untradeable. Evo Unlock Serge Gnabry Expires in 4 days 250 total 5 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -16894,17 +17064,17 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -16921,7 +17091,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Ilyas Ansah Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Ilyas Ansah! All rewards are untradeable. Ilyas Ansah Expires in 4 days 100 total 3 Objectives 58% 42%</t>
+          <t>Silver TOTS HM Ilyas Ansah Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Ilyas Ansah! All rewards are untradeable. Ilyas Ansah Expires in 3 days 100 total 3 Objectives 58% 42%</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -16931,17 +17101,17 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -16958,7 +17128,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 2 days 100 total 5 Objectives 82% 18%</t>
+          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 1 day 100 total 5 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -16968,17 +17138,17 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -16995,7 +17165,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 2 days 100 total 5 Objectives 91% 9%</t>
+          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 1 day 100 total 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -17005,17 +17175,17 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17032,7 +17202,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 2 days 100 total 5 Objectives 72% 28%</t>
+          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 1 day 100 total 5 Objectives 72% 28%</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -17042,17 +17212,17 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17069,7 +17239,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 2 days 100 total 3 Objectives 49% 51%</t>
+          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 1 day 100 total 3 Objectives 49% 51%</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -17079,17 +17249,17 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17313,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Nike Wildcard Challenge Complete the Nike Wildcard Challenge Objective group to earn Pack rewards and Vanity Items. All rewards are untradeable. 5X 82+ Rare Gold Players Pack Expires in 8 days 4 Objectives 22% 78%</t>
+          <t>Nike Wildcard Challenge Complete the Nike Wildcard Challenge Objective group to earn Pack rewards and Vanity Items. All rewards are untradeable. 5X 82+ Rare Gold Players Pack Expires in 7 days 4 Objectives 22% 78%</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -17153,17 +17323,17 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17890,7 +18060,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>SB_Report: 대상 모드 기준 핵심 수행 요약입니다. C열 관련 캠페인은 포스터 하단/작은 글씨용 근거로 활용할 수 있습니다.</t>
+          <t>SB_Report: 대상 모드 기준 핵심 수행 요약입니다. B열 내용 1개와 C열 관련 캠페인이 1:1로 대응되도록 펼쳐 표시합니다.</t>
         </is>
       </c>
     </row>
@@ -18242,12 +18412,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -18313,12 +18483,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -18384,12 +18554,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18455,12 +18625,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18526,12 +18696,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18597,12 +18767,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18668,12 +18838,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18739,12 +18909,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18810,12 +18980,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18881,12 +19051,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -18952,12 +19122,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -19023,12 +19193,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -19094,12 +19264,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -19165,12 +19335,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -19236,12 +19406,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -19307,12 +19477,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -19378,12 +19548,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -19449,12 +19619,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -20327,17 +20497,17 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -20420,17 +20590,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -20517,17 +20687,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -20610,17 +20780,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -20703,17 +20873,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -20796,17 +20966,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -20889,17 +21059,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -20982,17 +21152,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -21075,17 +21245,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -21176,17 +21346,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -21277,17 +21447,17 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -21378,17 +21548,17 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -21479,17 +21649,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -21580,17 +21750,17 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -21677,17 +21847,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -21774,17 +21944,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -21875,17 +22045,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -21976,17 +22146,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -22073,17 +22243,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -22170,17 +22340,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -22267,17 +22437,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -22364,17 +22534,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -22461,17 +22631,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -22558,17 +22728,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -22659,17 +22829,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -22760,17 +22930,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -22861,17 +23031,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -22962,17 +23132,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -23059,17 +23229,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -23160,17 +23330,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -23261,17 +23431,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -23362,17 +23532,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -23463,17 +23633,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -23564,17 +23734,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -23665,17 +23835,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -23766,17 +23936,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -23863,17 +24033,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -23960,17 +24130,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -24057,17 +24227,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -24154,17 +24324,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -32639,17 +32809,17 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -32732,17 +32902,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -32829,17 +32999,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -32922,17 +33092,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -33015,17 +33185,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -33108,17 +33278,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -33201,17 +33371,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -33294,17 +33464,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -33387,17 +33557,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -33488,17 +33658,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -33589,17 +33759,17 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -33690,17 +33860,17 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -33791,17 +33961,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -33892,17 +34062,17 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -33989,17 +34159,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T02:00+09:00</t>
+          <t>2026-05-11T02:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -34086,17 +34256,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -34187,17 +34357,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -34288,17 +34458,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11T02:00+09:00</t>
+          <t>2026-05-10T02:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -34385,17 +34555,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -34482,17 +34652,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -34579,17 +34749,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -34676,17 +34846,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -34773,17 +34943,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -34870,17 +35040,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -34971,17 +35141,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -35072,17 +35242,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -35173,17 +35343,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -35274,17 +35444,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -35371,17 +35541,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -35472,17 +35642,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -35573,17 +35743,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -35674,17 +35844,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -35775,17 +35945,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -35876,17 +36046,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -35977,17 +36147,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -36078,17 +36248,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 1 day</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/9 02:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09T02:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -36474,17 +36644,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -36571,17 +36741,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -36668,17 +36838,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -36765,17 +36935,17 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -602,8 +602,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)
-Evolution Revolution (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)
+Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 11:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 11:00)</t>
+          <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 11:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 11:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 11:00)</t>
+          <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 11:00)</t>
+          <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 11:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 11:00)</t>
+          <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
     </row>
@@ -5552,17 +5552,17 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -6007,17 +6007,17 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6098,17 +6098,17 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -6276,17 +6276,17 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -6458,17 +6458,17 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -6549,17 +6549,17 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -6640,17 +6640,17 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -6727,17 +6727,17 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -6814,17 +6814,17 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -7075,17 +7075,17 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>NEW Season 7 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 300 SP Expires in 6 days 1,050 total 3 of 5 Objectives 93% 7%</t>
+          <t>NEW Season 7 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 300 SP Expires in 6 days 1,050 total 3 of 5 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>NEW Silver TOTS HM Valentin Atangana Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Valentin Atangana! All rewards are untradeable. Valentin Atangana Expires in 6 days 100 total 3 Objectives 38% 62%</t>
+          <t>NEW Silver TOTS HM Valentin Atangana Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Valentin Atangana! All rewards are untradeable. Valentin Atangana Expires in 6 days 100 total 3 Objectives 37% 63%</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 9 hours 100 total 5 Objectives 73% 27%</t>
+          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 8 hours 100 total 5 Objectives 73% 27%</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -17422,17 +17422,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 9 hours 100 total 3 Objectives 49% 51%</t>
+          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 8 hours 100 total 3 Objectives 49% 51%</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -17459,17 +17459,17 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 9 hours 100 total 5 Objectives 91% 9%</t>
+          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 8 hours 100 total 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -17496,17 +17496,17 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 9 hours 100 total 5 Objectives 82% 18%</t>
+          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 8 hours 100 total 5 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -17533,17 +17533,17 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19187,12 +19187,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -19258,12 +19258,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -19329,12 +19329,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -19400,12 +19400,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -19471,12 +19471,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -19542,12 +19542,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -19613,12 +19613,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -19684,12 +19684,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -19755,12 +19755,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -19826,12 +19826,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -19897,12 +19897,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -22820,17 +22820,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -22921,17 +22921,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -23022,17 +23022,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -23123,17 +23123,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -23224,17 +23224,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -23325,17 +23325,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -23426,17 +23426,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -23527,17 +23527,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -23624,17 +23624,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -23725,17 +23725,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -23826,17 +23826,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -23927,17 +23927,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -24028,17 +24028,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -24125,17 +24125,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -24222,17 +24222,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -24319,17 +24319,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -24416,17 +24416,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -24513,17 +24513,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -36613,17 +36613,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -36714,17 +36714,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -36815,17 +36815,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -36916,17 +36916,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -37017,17 +37017,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -37118,17 +37118,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -37219,17 +37219,17 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -37320,17 +37320,17 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -37417,17 +37417,17 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -37518,17 +37518,17 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -37619,17 +37619,17 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -37720,17 +37720,17 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -37821,17 +37821,17 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -37918,17 +37918,17 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -38015,17 +38015,17 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -38112,17 +38112,17 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -38209,17 +38209,17 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -38306,17 +38306,17 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 hours</t>
+          <t>Expires in 8 hours</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>5/8 11:00</t>
+          <t>5/8 10:00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T11:00+09:00</t>
+          <t>2026-05-08T10:00+09:00</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -26,7 +26,7 @@
     <sheet name="How_To_Read" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$C$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$E$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SB_Action_Detail'!$A$1:$O$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New_Report_Index'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action_Plan'!$A$1:$U$64</definedName>
@@ -530,12 +530,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -554,6 +556,16 @@
           <t>관련 캠페인</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>신규여부</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>신규시트</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -571,6 +583,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -588,6 +606,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -606,6 +630,12 @@
 Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
@@ -619,6 +649,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -636,6 +672,12 @@
           <t>Silver TOTS HM Ilyas Ansah (마감 5/10 02:00)</t>
         </is>
       </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
@@ -649,6 +691,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -662,6 +710,12 @@
           <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
@@ -675,6 +729,12 @@
           <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -688,6 +748,12 @@
           <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
@@ -701,6 +767,12 @@
           <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
@@ -714,6 +786,12 @@
           <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
@@ -727,6 +805,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -744,6 +828,12 @@
           <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
@@ -757,6 +847,12 @@
           <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
@@ -770,6 +866,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
@@ -783,6 +885,12 @@
           <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -800,6 +908,12 @@
           <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
@@ -813,6 +927,12 @@
           <t>Silver TOTS HM Ilyas Ansah (마감 5/10 02:00)</t>
         </is>
       </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr"/>
@@ -826,6 +946,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr"/>
@@ -839,6 +965,12 @@
           <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr"/>
@@ -852,6 +984,12 @@
           <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -869,6 +1007,12 @@
           <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
@@ -882,6 +1026,12 @@
           <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr"/>
@@ -895,6 +1045,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
@@ -908,6 +1064,12 @@
           <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -925,6 +1087,12 @@
           <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
@@ -938,9 +1106,15 @@
           <t>Evolution Revolution (마감 5/8 10:00)</t>
         </is>
       </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C28"/>
+  <autoFilter ref="A1:E28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18400,7 +18574,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>latest/objectives_latest.xlsx의 Mission_DB와 비교해 새로 추가된 미션의 To do 항목에는 (신규미션)을 붙입니다. 선발/교체 요건은 신규로 생겼거나 요구 수량이 증가한 경우에만 표시합니다.</t>
+          <t>latest/objectives_latest.xlsx의 Mission_DB와 비교해 새로 추가된 미션은 SB_Report/New_Report의 신규여부=Y로 표시합니다. 선발/교체 요건은 신규로 생겼거나 요구 수량이 증가한 경우에만 Y로 표시합니다.</t>
         </is>
       </c>
     </row>
@@ -19970,10 +20144,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -626,8 +626,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)
-Evolution Revolution (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)
+Evolution Revolution (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 10:00)</t>
+          <t>Evolution Revolution (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 10:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 10:00)</t>
+          <t>Evolution Revolution (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 10:00)</t>
+          <t>Evolution Revolution (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 10:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 10:00)</t>
+          <t>Evolution Revolution (마감 5/8 05:00)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5908,17 +5908,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -6090,17 +6090,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -6181,17 +6181,17 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6272,17 +6272,17 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -6363,17 +6363,17 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -6450,17 +6450,17 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -6541,17 +6541,17 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -6723,17 +6723,17 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -6814,17 +6814,17 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -7075,17 +7075,17 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -7162,17 +7162,17 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 6 days 175 total 2 Objectives 92% 8%</t>
+          <t>NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 6 days 175 total 2 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>A Few of my Favourite Things Complete the challenges below to earn some of the community's favourite players to Evolve! Nico O'Reilly Expires in 21 days 4 Objectives 60% 40%</t>
+          <t>A Few of my Favourite Things Complete the challenges below to earn some of the community's favourite players to Evolve! Nico O'Reilly Expires in 21 days 4 Objectives 61% 39%</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 8 hours 100 total 5 Objectives 73% 27%</t>
+          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 3 hours 100 total 5 Objectives 73% 27%</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -17596,17 +17596,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 8 hours 100 total 3 Objectives 49% 51%</t>
+          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 3 hours 100 total 3 Objectives 49% 51%</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -17633,17 +17633,17 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17660,7 +17660,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 8 hours 100 total 5 Objectives 91% 9%</t>
+          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 3 hours 100 total 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -17670,17 +17670,17 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 8 hours 100 total 5 Objectives 82% 18%</t>
+          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 3 hours 100 total 5 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -17707,17 +17707,17 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19361,12 +19361,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -19432,12 +19432,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -19503,12 +19503,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -19574,12 +19574,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -19645,12 +19645,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -19716,12 +19716,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -19787,12 +19787,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -19858,12 +19858,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -19929,12 +19929,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -20071,12 +20071,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -22995,17 +22995,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -23096,17 +23096,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -23197,17 +23197,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -23298,17 +23298,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -23399,17 +23399,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -23500,17 +23500,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -23601,17 +23601,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -23702,17 +23702,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -23799,17 +23799,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -23900,17 +23900,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -24001,17 +24001,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -24102,17 +24102,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -24203,17 +24203,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -24300,17 +24300,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -24397,17 +24397,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -24494,17 +24494,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -24591,17 +24591,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -24688,17 +24688,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -36788,17 +36788,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -36889,17 +36889,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -36990,17 +36990,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -37091,17 +37091,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -37192,17 +37192,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -37293,17 +37293,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -37394,17 +37394,17 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -37495,17 +37495,17 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -37592,17 +37592,17 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -37693,17 +37693,17 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -37794,17 +37794,17 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -37895,17 +37895,17 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -37996,17 +37996,17 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -38093,17 +38093,17 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -38190,17 +38190,17 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -38287,17 +38287,17 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -38384,17 +38384,17 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -38481,17 +38481,17 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 hours</t>
+          <t>Expires in 3 hours</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>5/8 10:00</t>
+          <t>5/8 05:00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T10:00+09:00</t>
+          <t>2026-05-08T05:00+09:00</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -26,8 +26,8 @@
     <sheet name="How_To_Read" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$E$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SB_Action_Detail'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SB_Action_Detail'!$A$1:$O$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New_Report_Index'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action_Plan'!$A$1:$U$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Plan_Summary'!$A$1:$J$12</definedName>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -626,8 +626,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)
-Evolution Revolution (마감 5/8 05:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)
+Evolution Revolution (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 05:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 05:00)</t>
+          <t>Evolution Revolution (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -797,54 +797,54 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>USA ≥1</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>Uruguay ≥2</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>교체로 투입해도 가능</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>French</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Midfielder</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -858,12 +858,12 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -877,54 +877,54 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>Frauen-Bundesliga</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 05:00)</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>To do (득점)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Saudi Arabia: Goal 10회</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Germany: 2경기 각 Goal 1회</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Silver TOTS HM Ilyas Ansah (마감 5/10 02:00)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -938,12 +938,12 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CONMEBOL Libertadores: 5경기 각 Goal 1회</t>
+          <t>Germany: 2경기 각 Goal 1회</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
+          <t>Silver TOTS HM Ilyas Ansah (마감 5/10 02:00)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -957,12 +957,12 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Frauen-Bundesliga: 2경기 각 Goal 1회</t>
+          <t>CONMEBOL Libertadores: 5경기 각 Goal 1회</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 05:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -976,35 +976,31 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>Frauen-Bundesliga: 2경기 각 Goal 1회</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>TOTS: Outside Box Goal 5회</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Evolution Revolution (마감 5/8 05:00)</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>To do (어시스트)</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>French: Assist 4회</t>
-        </is>
-      </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
+          <t>Evolution Revolution (마감 5/8 04:00)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1018,12 +1014,12 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Midfielder: Assist 4회</t>
+          <t>USA: Goal 3회</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1037,12 +1033,12 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Defender: Assist 4회</t>
+          <t>USA: Goal 5회</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1053,15 +1049,19 @@
       <c r="E25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>To do (어시스트)</t>
+        </is>
+      </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
+          <t>French: Assist 4회</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 05:00)</t>
+          <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1072,19 +1072,15 @@
       <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>To do (기타)</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Clean Sheet 4</t>
+          <t>Midfielder: Assist 4회</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 05:00)</t>
+          <t>TOTS HM Musab Al-Juwair (마감 5/11 02:00)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1098,23 +1094,84 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>Defender: Assist 4회</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Evolution Revolution (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>To do (기타)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Clean Sheet 4</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>Clean Sheet 5</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Evolution Revolution (마감 5/8 05:00)</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Evolution Revolution (마감 5/8 04:00)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E28"/>
+  <autoFilter ref="A1:E31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5726,17 +5783,17 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5817,17 +5874,17 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5908,17 +5965,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -5999,17 +6056,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -6090,17 +6147,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -6181,17 +6238,17 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6272,17 +6329,17 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -6363,17 +6420,17 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -6450,17 +6507,17 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -6541,17 +6598,17 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -6632,17 +6689,17 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -6723,17 +6780,17 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -6814,17 +6871,17 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -6901,17 +6958,17 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -6988,17 +7045,17 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -7075,17 +7132,17 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -7162,17 +7219,17 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -7249,17 +7306,17 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -17290,7 +17347,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>NEW Weekly Objectives Complete weekly Objectives to earn SP! 375 SP Expires in 6 days 1,500 total 5 Objectives 95% 5%</t>
+          <t>NEW Weekly Objectives Complete weekly Objectives to earn SP! 375 SP Expires in 6 days 1,500 total 5 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -17327,7 +17384,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>NEW Silver TOTS HM Valentin Atangana Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Valentin Atangana! All rewards are untradeable. Valentin Atangana Expires in 6 days 100 total 3 Objectives 37% 63%</t>
+          <t>NEW Silver TOTS HM Valentin Atangana Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Valentin Atangana! All rewards are untradeable. Valentin Atangana Expires in 6 days 100 total 3 Objectives 36% 64%</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -17586,7 +17643,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 3 hours 100 total 5 Objectives 73% 27%</t>
+          <t>TOTS HM Sebastián Coates Complete the challenges below to earn SP, Pack rewards, a Cosmetic Evolution, and TOTS Honourable Mentions Sebastián Coates! Sebastián Coates Expires in 2 hours 100 total 5 Objectives 73% 27%</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -17596,17 +17653,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17680,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 3 hours 100 total 3 Objectives 49% 51%</t>
+          <t>Silver TOTS HM Lotta Wrede Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Lotta Wrede! All rewards are untradeable. Lotta Wrede Expires in 2 hours 100 total 3 Objectives 49% 51%</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -17633,17 +17690,17 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17660,7 +17717,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 3 hours 100 total 5 Objectives 91% 9%</t>
+          <t>Evolution Revolution Complete the challenges below to earn EVO consumables and SP! 5X 83+ Rare Gold Players Pack Expires in 2 hours 100 total 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -17670,17 +17727,17 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17754,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 3 hours 100 total 5 Objectives 82% 18%</t>
+          <t>Bundesliga TOTS Exhibition Complete this objective to earn Pack rewards, SP, Evolutions, a Bundesliga / Frauen-Bundesliga TOTS Guarantee pack, and TOTS Honourable Mentions Fisnik Asllani and Andrej Kramarić. All rewards are untradeable. Bl/Gpfbl Tots Player Pack Fisnik Asllani Andrej Kramarić Expires in 2 hours 100 total 5 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -17707,17 +17764,17 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18732,17 +18789,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Assist 4</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ROSHN Saudi League ≥1</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -18752,7 +18809,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>French: Assist 4회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -18762,22 +18819,18 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+      <c r="O2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr"/>
@@ -18803,17 +18856,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>Assist 4</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>ROSHN Saudi League ≥1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>French</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -18823,7 +18876,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>French: Assist 4회</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -18833,11 +18886,11 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -18859,27 +18912,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives</t>
+          <t>Silver TOTS HM Valentin Atangana - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Play 6</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia ≥1</t>
+          <t>ROSHN Saudi League ≥1</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -18904,11 +18957,11 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Play 6</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -18930,22 +18983,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives</t>
+          <t>A Few of my Favourite Things - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5/11 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Assist 4</t>
+          <t>Play 5 Live Events</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -18955,7 +19008,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -18965,7 +19018,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Midfielder: Assist 4회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -18975,22 +19028,18 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
@@ -19016,12 +19065,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Keep It Tight</t>
+          <t>Play 6</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>ROSHN Saudi Pro League ≥1</t>
+          <t>Saudi Arabia ≥1</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -19046,15 +19095,15 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Play 6</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -19087,17 +19136,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Win 6</t>
+          <t>Assist 4</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia ≥2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -19107,7 +19156,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Midfielder: Assist 4회</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -19117,11 +19166,11 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Win 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -19158,22 +19207,22 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Keep It Tight</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ROSHN Saudi Pro League ≥1</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia: Goal 10회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -19196,7 +19245,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -19214,27 +19263,27 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives</t>
+          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5/10 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>Win 6</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Bundesliga ≥1</t>
+          <t>Saudi Arabia ≥2</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -19259,11 +19308,11 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>Win 6</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
@@ -19285,22 +19334,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives</t>
+          <t>TOTS HM Musab Al-Juwair - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>5/10 02:00</t>
+          <t>5/11 02:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Score in 2</t>
+          <t>Score 10</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -19310,12 +19359,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Germany: 2경기 각 Goal 1회</t>
+          <t>Saudi Arabia: Goal 10회</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -19334,11 +19383,11 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -19356,37 +19405,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives</t>
+          <t>Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Score in 5</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bundesliga ≥1</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>CONMEBOL Libertadores</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>CONMEBOL Libertadores: 5경기 각 Goal 1회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -19401,15 +19450,15 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -19427,37 +19476,37 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives</t>
+          <t>Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Win 7</t>
+          <t>Score in 2</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Uruguay ≥2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Germany: 2경기 각 Goal 1회</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -19472,15 +19521,15 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Win 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -19498,27 +19547,27 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives</t>
+          <t>Silver TOTS HM Ilyas Ansah - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/10 02:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>4 Clean sheets</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>CONMEBOL Libertadores ≥1</t>
+          <t>Bundesliga ≥1</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -19538,27 +19587,23 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Clean Sheet 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+      <c r="O13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -19574,17 +19619,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Assist 4</t>
+          <t>Score in 5</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -19594,17 +19639,17 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>CONMEBOL Libertadores</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CONMEBOL Libertadores: 5경기 각 Goal 1회</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Defender: Assist 4회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -19618,11 +19663,11 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -19645,22 +19690,22 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Win 7</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Uruguay ≥1</t>
+          <t>Uruguay ≥2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -19685,11 +19730,11 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Win 7</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
@@ -19711,27 +19756,27 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives</t>
+          <t>TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>4 Clean sheets</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Germany ≥1</t>
+          <t>CONMEBOL Libertadores ≥1</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -19751,16 +19796,16 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Clean Sheet 4</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -19782,22 +19827,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives</t>
+          <t>TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Score in 2</t>
+          <t>Assist 4</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -19807,17 +19852,17 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Frauen-Bundesliga</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Frauen-Bundesliga: 2경기 각 Goal 1회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Defender: Assist 4회</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -19831,11 +19876,11 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -19853,27 +19898,27 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+          <t>TOTS HM Sebastián Coates - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Turbo Strength</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>TOTS ≥1</t>
+          <t>Uruguay ≥1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -19898,11 +19943,11 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Win 7</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -19924,32 +19969,32 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+          <t>Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Pass IQ</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Germany ≥1</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>TOTS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -19959,7 +20004,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -19969,15 +20014,15 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -19995,22 +20040,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+          <t>Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>From Distance</t>
+          <t>Score in 2</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -20020,12 +20065,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>TOTS</t>
+          <t>Frauen-Bundesliga</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>TOTS: Outside Box Goal 5회</t>
+          <t>Frauen-Bundesliga: 2경기 각 Goal 1회</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -20044,11 +20089,11 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -20066,70 +20111,685 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
+          <t>Silver TOTS HM Lotta Wrede - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 hours</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>5/8 04:00</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Play 2</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Germany ≥1</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Play 2</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
           <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 3 hours</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>5/8 05:00</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 hours</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>5/8 04:00</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Turbo Strength</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>TOTS ≥1</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Win 7</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 hours</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>5/8 04:00</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Pass IQ</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>TOTS</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>TOTS: 1경기 각 Through Ball Assist 1회</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 hours</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>5/8 04:00</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>From Distance</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>TOTS</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>TOTS: Outside Box Goal 5회</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 hours</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>5/8 04:00</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Defensive Instinct</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>TOTS ≥1</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Clean Sheet 5</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>Min. Semi-Pro</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Evolution Revolution - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 2 hours</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>5/8 04:00</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Play 5</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Nike Wildcard Challenge - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>5/14 02:00</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Score 3</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>USA: Goal 3회</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Nike Wildcard Challenge - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>5/14 02:00</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Score 5</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>USA: Goal 5회</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Nike Wildcard Challenge - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>5/14 02:00</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Win 3</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>USA ≥1</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Win 3</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Nike Wildcard Challenge - EA SPORTS FC 26 Objectives</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 6 days</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>5/14 02:00</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Play 3</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>USA ≥1</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Play 3</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22995,17 +23655,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -23096,17 +23756,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -23197,17 +23857,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -23298,17 +23958,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -23399,17 +24059,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -23500,17 +24160,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -23601,17 +24261,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -23702,17 +24362,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -23799,17 +24459,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -23900,17 +24560,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -24001,17 +24661,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -24102,17 +24762,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -24203,17 +24863,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -24300,17 +24960,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -24397,17 +25057,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -24494,17 +25154,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -24591,17 +25251,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -24688,17 +25348,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -36788,17 +37448,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -36889,17 +37549,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -36990,17 +37650,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -37091,17 +37751,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -37192,17 +37852,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -37293,17 +37953,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -37394,17 +38054,17 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -37495,17 +38155,17 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -37592,17 +38252,17 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -37693,17 +38353,17 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -37794,17 +38454,17 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -37895,17 +38555,17 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -37996,17 +38656,17 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -38093,17 +38753,17 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -38190,17 +38850,17 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -38287,17 +38947,17 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -38384,17 +39044,17 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -38481,17 +39141,17 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 hours</t>
+          <t>Expires in 2 hours</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>5/8 05:00</t>
+          <t>5/8 04:00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T05:00+09:00</t>
+          <t>2026-05-08T04:00+09:00</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -626,8 +626,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)
-Evolution Revolution (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)
+Evolution Revolution (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 04:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 04:00)</t>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 04:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Lotta Wrede (마감 5/8 04:00)</t>
+          <t>Silver TOTS HM Lotta Wrede (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 04:00)</t>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 04:00)</t>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Sebastián Coates (마감 5/8 04:00)</t>
+          <t>TOTS HM Sebastián Coates (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Evolution Revolution (마감 5/8 04:00)</t>
+          <t>Evolution Revolution (마감 5/8 02:00)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -17658,12 +17658,12 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17695,12 +17695,12 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17732,12 +17732,12 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -20050,7 +20050,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -20330,7 +20330,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -23660,12 +23660,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -23761,12 +23761,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -23862,12 +23862,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -24165,12 +24165,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -24266,12 +24266,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -24367,12 +24367,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -24464,12 +24464,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -24565,12 +24565,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -24767,12 +24767,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -24868,12 +24868,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -24965,12 +24965,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -25062,12 +25062,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -25159,12 +25159,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -25256,12 +25256,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -25353,12 +25353,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -37453,12 +37453,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -37554,12 +37554,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -37655,12 +37655,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -37756,12 +37756,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -37857,12 +37857,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -37958,12 +37958,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -38059,12 +38059,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -38160,12 +38160,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -38257,12 +38257,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -38358,12 +38358,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -38459,12 +38459,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -38560,12 +38560,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -38661,12 +38661,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -38758,12 +38758,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -38855,12 +38855,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -38952,12 +38952,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -39049,12 +39049,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -39146,12 +39146,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>5/8 04:00</t>
+          <t>5/8 02:00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08T04:00+09:00</t>
+          <t>2026-05-08T02:00+09:00</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -4422,17 +4422,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -10244,17 +10244,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10517,17 +10517,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -10608,17 +10608,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 17 hours 100 total 4 of 5 Objectives 56% 44%</t>
+          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 16 hours 100 total 4 of 5 Objectives 56% 44%</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -19605,17 +19605,17 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 18 hours 5 Objectives 18% 82%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 17 hours 5 Objectives 18% 82%</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -20086,17 +20086,17 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
     </row>
@@ -24857,17 +24857,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -24954,17 +24954,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -25051,17 +25051,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -25148,17 +25148,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -25245,17 +25245,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -29703,17 +29703,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -29800,17 +29800,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -29897,17 +29897,17 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -29994,17 +29994,17 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -30091,17 +30091,17 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -30188,17 +30188,17 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -39032,17 +39032,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -39129,17 +39129,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -39226,17 +39226,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -39323,17 +39323,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -39420,17 +39420,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -45345,17 +45345,17 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -45442,17 +45442,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -45539,17 +45539,17 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -45636,17 +45636,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -45733,17 +45733,17 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -45830,17 +45830,17 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 hours</t>
+          <t>Expires in 17 hours</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>5/12 20:00</t>
+          <t>5/12 19:00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T20:00+09:00</t>
+          <t>2026-05-12T19:00+09:00</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -4422,17 +4422,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -10244,17 +10244,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10517,17 +10517,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -10608,17 +10608,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 16 hours 100 total 4 of 5 Objectives 56% 44%</t>
+          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 15 hours 100 total 4 of 5 Objectives 56% 44%</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -19605,17 +19605,17 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 17 hours 5 Objectives 18% 82%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 16 hours 5 Objectives 18% 82%</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -20086,17 +20086,17 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
     </row>
@@ -24857,17 +24857,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -24954,17 +24954,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -25051,17 +25051,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -25148,17 +25148,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -25245,17 +25245,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -29703,17 +29703,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -29800,17 +29800,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -29897,17 +29897,17 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -29994,17 +29994,17 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -30091,17 +30091,17 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -30188,17 +30188,17 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -39032,17 +39032,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -39129,17 +39129,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -39226,17 +39226,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -39323,17 +39323,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -39420,17 +39420,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 15 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 17:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T17:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -45345,17 +45345,17 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -45442,17 +45442,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -45539,17 +45539,17 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -45636,17 +45636,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -45733,17 +45733,17 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -45830,17 +45830,17 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 hours</t>
+          <t>Expires in 16 hours</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>5/12 19:00</t>
+          <t>5/12 18:00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T19:00+09:00</t>
+          <t>2026-05-12T18:00+09:00</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -4422,17 +4422,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -10244,17 +10244,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10517,17 +10517,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -10608,17 +10608,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>NEW TOTS HM: Florent Hadergjonaj Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Florent Hadergjonaj! All rewards are untradeable. Florent Hadergjonaj Expires in 7 days 100 total 5 Objectives 27% 73%</t>
+          <t>NEW TOTS HM: Florent Hadergjonaj Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Florent Hadergjonaj! All rewards are untradeable. Florent Hadergjonaj Expires in 7 days 100 total 5 Objectives 28% 73%</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>NEW Ultimate Gauntlet 17 Complete 9 of 10 challenges in the Ultimate Gauntlet 17 to earn exclusive rewards! All rewards are untradeable. 10X 86+ Rare Gold Players Pack Expires in 7 days 9 of 10 Objectives 76% 24%</t>
+          <t>NEW Ultimate Gauntlet 17 Complete 9 of 10 challenges in the Ultimate Gauntlet 17 to earn exclusive rewards! All rewards are untradeable. 10X 86+ Rare Gold Players Pack Expires in 7 days 9 of 10 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 15 hours 100 total 4 of 5 Objectives 56% 44%</t>
+          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 13 hours 100 total 4 of 5 Objectives 56% 44%</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -19605,17 +19605,17 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 16 hours 5 Objectives 18% 82%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 14 hours 5 Objectives 18% 82%</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -20086,17 +20086,17 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
     </row>
@@ -24857,17 +24857,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -24954,17 +24954,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -25051,17 +25051,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -25148,17 +25148,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -25245,17 +25245,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -29703,17 +29703,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -29800,17 +29800,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -29897,17 +29897,17 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -29994,17 +29994,17 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -30091,17 +30091,17 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -30188,17 +30188,17 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -39032,17 +39032,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -39129,17 +39129,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -39226,17 +39226,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -39323,17 +39323,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -39420,17 +39420,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 hours</t>
+          <t>Expires in 13 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 17:00</t>
+          <t>5/12 15:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T17:00+09:00</t>
+          <t>2026-05-12T15:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -45345,17 +45345,17 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -45442,17 +45442,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -45539,17 +45539,17 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -45636,17 +45636,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -45733,17 +45733,17 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -45830,17 +45830,17 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 hours</t>
+          <t>Expires in 14 hours</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>5/12 18:00</t>
+          <t>5/12 16:00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00+09:00</t>
+          <t>2026-05-12T16:00+09:00</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Maureen Cosson (마감 5/18 02:00)</t>
+          <t>Silver TOTS HM Maureen Cosson (마감 5/17 02:00)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM: Arsène Kouassi (마감 5/16 02:00)</t>
+          <t>Silver TOTS HM: Arsène Kouassi (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Valentin Atangana (마감 5/15 02:00)</t>
+          <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM: Arsène Kouassi (마감 5/16 02:00)</t>
+          <t>Silver TOTS HM: Arsène Kouassi (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Maureen Cosson (마감 5/18 02:00)</t>
+          <t>Silver TOTS HM Maureen Cosson (마감 5/17 02:00)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM: Arsène Kouassi (마감 5/16 02:00)</t>
+          <t>Silver TOTS HM: Arsène Kouassi (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Nike Wildcard Challenge (마감 5/15 02:00)</t>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Nike Wildcard Challenge (마감 5/15 02:00)</t>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Maureen Cosson (마감 5/18 02:00)</t>
+          <t>Silver TOTS HM Maureen Cosson (마감 5/17 02:00)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Valentin Atangana (마감 5/15 02:00)</t>
+          <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: Florent Hadergjonaj (마감 5/19 02:00)</t>
+          <t>TOTS HM: Florent Hadergjonaj (마감 5/18 02:00)</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Maureen Cosson (마감 5/18 02:00)</t>
+          <t>Silver TOTS HM Maureen Cosson (마감 5/17 02:00)</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Maureen Cosson (마감 5/18 02:00)</t>
+          <t>Silver TOTS HM Maureen Cosson (마감 5/17 02:00)</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM: Arsène Kouassi (마감 5/16 02:00)</t>
+          <t>Silver TOTS HM: Arsène Kouassi (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM: Arsène Kouassi (마감 5/16 02:00)</t>
+          <t>Silver TOTS HM: Arsène Kouassi (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind (마감 5/16 02:00)</t>
+          <t>TOTS HM: NWSL Grind (마감 5/15 02:00)</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Valentin Atangana (마감 5/15 02:00)</t>
+          <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Valentin Atangana (마감 5/15 02:00)</t>
+          <t>Silver TOTS HM Valentin Atangana (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Nike Wildcard Challenge (마감 5/15 02:00)</t>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Nike Wildcard Challenge (마감 5/15 02:00)</t>
+          <t>Nike Wildcard Challenge (마감 5/14 02:00)</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -2721,17 +2721,17 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -3793,17 +3793,17 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -3880,17 +3880,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -3967,17 +3967,17 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -4054,17 +4054,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -4236,17 +4236,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -4422,17 +4422,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -4952,17 +4952,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -5043,17 +5043,17 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -5134,17 +5134,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -5743,17 +5743,17 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -5834,17 +5834,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -6012,17 +6012,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -6186,17 +6186,17 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -6273,17 +6273,17 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -6360,17 +6360,17 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -6542,17 +6542,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -6724,17 +6724,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -6815,17 +6815,17 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6906,17 +6906,17 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -7432,17 +7432,17 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -7709,17 +7709,17 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -7800,17 +7800,17 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -7986,17 +7986,17 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -8077,17 +8077,17 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -8164,17 +8164,17 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -8251,17 +8251,17 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -8429,17 +8429,17 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -8603,17 +8603,17 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -8690,17 +8690,17 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -8777,17 +8777,17 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -8864,17 +8864,17 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -8951,17 +8951,17 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -9038,17 +9038,17 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -9220,17 +9220,17 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -9311,17 +9311,17 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -9568,17 +9568,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -9655,17 +9655,17 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -9738,17 +9738,17 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -9821,17 +9821,17 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -9904,17 +9904,17 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -9987,17 +9987,17 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -10244,17 +10244,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10517,17 +10517,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -10608,17 +10608,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -10786,17 +10786,17 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -10873,17 +10873,17 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -10960,17 +10960,17 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>NEW TOTS HM: Florent Hadergjonaj Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Florent Hadergjonaj! All rewards are untradeable. Florent Hadergjonaj Expires in 7 days 100 total 5 Objectives 28% 73%</t>
+          <t>NEW TOTS HM: Florent Hadergjonaj Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Florent Hadergjonaj! All rewards are untradeable. Florent Hadergjonaj Expires in 6 days 100 total 5 Objectives 27% 73%</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -19457,17 +19457,17 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>NEW Ultimate Gauntlet 17 Complete 9 of 10 challenges in the Ultimate Gauntlet 17 to earn exclusive rewards! All rewards are untradeable. 10X 86+ Rare Gold Players Pack Expires in 7 days 9 of 10 Objectives 77% 23%</t>
+          <t>NEW Ultimate Gauntlet 17 Complete 9 of 10 challenges in the Ultimate Gauntlet 17 to earn exclusive rewards! All rewards are untradeable. 10X 86+ Rare Gold Players Pack Expires in 6 days 9 of 10 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -19494,17 +19494,17 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19521,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>NEW Ultimate Gauntlet 17 Bonus Compete in the Ultimate Gauntlet 17 to earn bonus rewards! All rewards are untradeable. L1/Apl/Nwsl Tots Player Pack Expires in 7 days 4 Objectives 74% 26%</t>
+          <t>NEW Ultimate Gauntlet 17 Bonus Compete in the Ultimate Gauntlet 17 to earn bonus rewards! All rewards are untradeable. L1/Apl/Nwsl Tots Player Pack Expires in 6 days 4 Objectives 73% 27%</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -19531,17 +19531,17 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Maureen Cosson Complete this objective to earn SP, Packs, and Silver TOTS HM Maureen Cosson! All rewards are untradeable. Maureen Cosson Expires in 6 days 100 total 3 Objectives 12% 88%</t>
+          <t>Silver TOTS HM Maureen Cosson Complete this objective to earn SP, Packs, and Silver TOTS HM Maureen Cosson! All rewards are untradeable. Maureen Cosson Expires in 5 days 100 total 3 Objectives 12% 88%</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -19568,17 +19568,17 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 13 hours 100 total 4 of 5 Objectives 56% 44%</t>
+          <t>French TOTS Flash Rush Join the "French TOTS" Flash Rush event and complete 4 of 5 challenges to earn Pack rewards, an Evolution and SP! All rewards are untradeable. 10X 82+ Rare Gold Players Pack Expires in 10 hours 100 total 4 of 5 Objectives 56% 44%</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -19605,17 +19605,17 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>TOTS Daily Login Completionist Complete the TOTS Daily Login Upgrade SBCs to earn additional packs and a TOTS Cosmetic EVO! All rewards are untradeable. 10X 83+ Rare Gold Players Pack Expires in 18 days 6 Objectives 64% 36%</t>
+          <t>TOTS Daily Login Completionist Complete the TOTS Daily Login Upgrade SBCs to earn additional packs and a TOTS Cosmetic EVO! All rewards are untradeable. 10X 83+ Rare Gold Players Pack Expires in 17 days 6 Objectives 64% 36%</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -19642,17 +19642,17 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM: Arsène Kouassi Complete the challenges below to earn SP, packs and Silver TOTS HM Arsène Kouassi! All rewards are untradeable. Arsène Kouassi Expires in 4 days 100 total 3 Objectives 67% 33%</t>
+          <t>Silver TOTS HM: Arsène Kouassi Complete the challenges below to earn SP, packs and Silver TOTS HM Arsène Kouassi! All rewards are untradeable. Arsène Kouassi Expires in 3 days 100 total 3 Objectives 67% 33%</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -19716,17 +19716,17 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19743,7 +19743,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Ligue 1 TOTS Exhibition Complete the challenges below to earn Pack rewards, Evolutions, a Ligue 1/Arkema Première Ligue/NWSL TOTS Guarantee Pack and TOTS Honourable Mentions Niakhaté and Rongier. All rewards are untradeable. L1/Apl/Nwsl Tots Player Pack Moussa Niakhaté Valentin Rongier Expires in 4 days 500 total 5 Objectives 83% 17%</t>
+          <t>Ligue 1 TOTS Exhibition Complete the challenges below to earn Pack rewards, Evolutions, a Ligue 1/Arkema Première Ligue/NWSL TOTS Guarantee Pack and TOTS Honourable Mentions Niakhaté and Rongier. All rewards are untradeable. L1/Apl/Nwsl Tots Player Pack Moussa Niakhaté Valentin Rongier Expires in 3 days 500 total 5 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -19753,17 +19753,17 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TOTS Puzzle Completionist Complete the TOTS Puzzle SBCs to earn additional packs and a TOTS Cosmetic EVO! All rewards are untradeable. 20X 82+ Rare Gold Players Pack Expires in 6 days 7 Objectives 82% 18%</t>
+          <t>TOTS Puzzle Completionist Complete the TOTS Puzzle SBCs to earn additional packs and a TOTS Cosmetic EVO! All rewards are untradeable. 20X 82+ Rare Gold Players Pack Expires in 5 days 7 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -19790,17 +19790,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>TOTS HM: NWSL Grind Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Taylor Flint and Emma Sears! All rewards are untradeable. Emma Sears Expires in 4 days 100 total 5 Objectives 77% 23%</t>
+          <t>TOTS HM: NWSL Grind Complete the challenges below to earn SP, pack rewards, a cosmetic evolution, and TOTS Honourable Mentions Taylor Flint and Emma Sears! All rewards are untradeable. Emma Sears Expires in 3 days 100 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -19864,17 +19864,17 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 375 SP Expires in 3 days 1,500 total 5 Objectives 96% 4%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 375 SP Expires in 2 days 1,500 total 5 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -19901,17 +19901,17 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Season 7 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 300 SP Expires in 3 days 1,050 total 3 of 5 Objectives 94% 6%</t>
+          <t>Season 7 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 300 SP Expires in 2 days 1,050 total 3 of 5 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -19938,17 +19938,17 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Valentin Atangana Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Valentin Atangana! All rewards are untradeable. Valentin Atangana Expires in 3 days 100 total 3 Objectives 36% 64%</t>
+          <t>Silver TOTS HM Valentin Atangana Complete this objective to earn SP, Coin Boost, and Silver TOTS HM Valentin Atangana! All rewards are untradeable. Valentin Atangana Expires in 2 days 100 total 3 Objectives 36% 64%</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -19975,17 +19975,17 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 175 total 2 Objectives 92% 8%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 175 total 2 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -20012,17 +20012,17 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>A Few of my Favourite Things Complete the challenges below to earn some of the community's favourite players to Evolve! Nico O'Reilly Expires in 18 days 4 Objectives 61% 39%</t>
+          <t>A Few of my Favourite Things Complete the challenges below to earn some of the community's favourite players to Evolve! Nico O'Reilly Expires in 17 days 4 Objectives 61% 39%</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -20049,17 +20049,17 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 14 hours 5 Objectives 18% 82%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 88+ Rare Gold Player Pack Expires in 11 hours 5 Objectives 18% 82%</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -20086,17 +20086,17 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Nike Wildcard Challenge Complete the Nike Wildcard Challenge Objective group to earn Pack rewards and Vanity Items. All rewards are untradeable. 5X 82+ Rare Gold Players Pack Expires in 3 days 4 Objectives 22% 78%</t>
+          <t>Nike Wildcard Challenge Complete the Nike Wildcard Challenge Objective group to earn Pack rewards and Vanity Items. All rewards are untradeable. 5X 82+ Rare Gold Players Pack Expires in 2 days 4 Objectives 22% 78%</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -20123,17 +20123,17 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20952,12 +20952,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -21023,12 +21023,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -21094,12 +21094,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -21165,12 +21165,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -21307,12 +21307,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -21378,12 +21378,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -21449,12 +21449,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -21516,12 +21516,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -21583,12 +21583,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -21654,12 +21654,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -21725,12 +21725,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -21796,12 +21796,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -21867,12 +21867,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -21938,12 +21938,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -22009,12 +22009,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -22080,12 +22080,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -22147,12 +22147,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -22289,12 +22289,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -22356,12 +22356,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -22423,12 +22423,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -22490,12 +22490,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -22889,17 +22889,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -22990,17 +22990,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -23091,17 +23091,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -23192,17 +23192,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -23293,17 +23293,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -23394,17 +23394,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -23491,17 +23491,17 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -23588,17 +23588,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -23685,17 +23685,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -23782,17 +23782,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -23879,17 +23879,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -23976,17 +23976,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -24073,17 +24073,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -24170,17 +24170,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -24267,17 +24267,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -24364,17 +24364,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -24461,17 +24461,17 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -24558,17 +24558,17 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -24659,17 +24659,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -24760,17 +24760,17 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -24857,17 +24857,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -24954,17 +24954,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -25051,17 +25051,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -25148,17 +25148,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -25245,17 +25245,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -25342,17 +25342,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -25439,17 +25439,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -25536,17 +25536,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -25633,17 +25633,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -25730,17 +25730,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -25827,17 +25827,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -26203,17 +26203,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -26300,17 +26300,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -26401,17 +26401,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -26502,17 +26502,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -26599,17 +26599,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -26696,17 +26696,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -26793,17 +26793,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -26890,17 +26890,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -26987,17 +26987,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -27084,17 +27084,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -27181,17 +27181,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -27278,17 +27278,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -27375,17 +27375,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -27472,17 +27472,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -27569,17 +27569,17 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -28151,17 +28151,17 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -28252,17 +28252,17 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -28353,17 +28353,17 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -28454,17 +28454,17 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -28555,17 +28555,17 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -28656,17 +28656,17 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -28753,17 +28753,17 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -28854,17 +28854,17 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -28955,17 +28955,17 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -29048,17 +29048,17 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -29145,17 +29145,17 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -29238,17 +29238,17 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -29331,17 +29331,17 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -29424,17 +29424,17 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -29517,17 +29517,17 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -29610,17 +29610,17 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -29703,17 +29703,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -29800,17 +29800,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -29897,17 +29897,17 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -29994,17 +29994,17 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -30091,17 +30091,17 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -30188,17 +30188,17 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -30285,17 +30285,17 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -30382,17 +30382,17 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -30479,17 +30479,17 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -30576,17 +30576,17 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -33383,17 +33383,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -33484,17 +33484,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -33585,17 +33585,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -33682,17 +33682,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -33779,17 +33779,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -33880,17 +33880,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -33977,17 +33977,17 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -34074,17 +34074,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -34171,17 +34171,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -34268,17 +34268,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -34365,17 +34365,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -34462,17 +34462,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -34559,17 +34559,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -34656,17 +34656,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -34753,17 +34753,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -37064,17 +37064,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -37165,17 +37165,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -37266,17 +37266,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -37367,17 +37367,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -37468,17 +37468,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -37569,17 +37569,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -37666,17 +37666,17 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -37763,17 +37763,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -37860,17 +37860,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -37957,17 +37957,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -38054,17 +38054,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -38151,17 +38151,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -38248,17 +38248,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -38345,17 +38345,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -38442,17 +38442,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -38539,17 +38539,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -38636,17 +38636,17 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>5/19 02:00</t>
+          <t>5/18 02:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T02:00+09:00</t>
+          <t>2026-05-18T02:00+09:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -38733,17 +38733,17 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -38834,17 +38834,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -38935,17 +38935,17 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -39032,17 +39032,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -39129,17 +39129,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -39226,17 +39226,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -39323,17 +39323,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -39420,17 +39420,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 hours</t>
+          <t>Expires in 10 hours</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5/12 15:00</t>
+          <t>5/12 12:00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T15:00+09:00</t>
+          <t>2026-05-12T12:00+09:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -39517,17 +39517,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -39614,17 +39614,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -39711,17 +39711,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -39808,17 +39808,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -39905,17 +39905,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -40002,17 +40002,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -40378,17 +40378,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -40475,17 +40475,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -40576,17 +40576,17 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -40677,17 +40677,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -40774,17 +40774,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -40871,17 +40871,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -40968,17 +40968,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -41065,17 +41065,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -41162,17 +41162,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -41259,17 +41259,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -41356,17 +41356,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -41453,17 +41453,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -41550,17 +41550,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -41647,17 +41647,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -41744,17 +41744,17 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5/18 02:00</t>
+          <t>5/17 02:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:00+09:00</t>
+          <t>2026-05-17T02:00+09:00</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -42326,17 +42326,17 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -42427,17 +42427,17 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -42528,17 +42528,17 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -42629,17 +42629,17 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -42730,17 +42730,17 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>5/16 02:00</t>
+          <t>5/15 02:00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-16T02:00+09:00</t>
+          <t>2026-05-15T02:00+09:00</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -42831,17 +42831,17 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -42932,17 +42932,17 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -43033,17 +43033,17 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -43130,17 +43130,17 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -43227,17 +43227,17 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -43328,17 +43328,17 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -43425,17 +43425,17 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -43522,17 +43522,17 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -43619,17 +43619,17 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -43716,17 +43716,17 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -43813,17 +43813,17 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -43910,17 +43910,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -44007,17 +44007,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -44104,17 +44104,17 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -44201,17 +44201,17 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -44302,17 +44302,17 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -44403,17 +44403,17 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -44500,17 +44500,17 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -44597,17 +44597,17 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -44690,17 +44690,17 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -44787,17 +44787,17 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -44880,17 +44880,17 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -44973,17 +44973,17 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -45066,17 +45066,17 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -45159,17 +45159,17 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -45252,17 +45252,17 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Expires in 18 days</t>
+          <t>Expires in 17 days</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>5/30 02:00</t>
+          <t>5/29 02:00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30T02:00+09:00</t>
+          <t>2026-05-29T02:00+09:00</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -45345,17 +45345,17 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -45442,17 +45442,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -45539,17 +45539,17 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -45636,17 +45636,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -45733,17 +45733,17 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -45830,17 +45830,17 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Expires in 14 hours</t>
+          <t>Expires in 11 hours</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>5/12 16:00</t>
+          <t>5/12 13:00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12T16:00+09:00</t>
+          <t>2026-05-12T13:00+09:00</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -45927,17 +45927,17 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -46024,17 +46024,17 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -46121,17 +46121,17 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -46218,17 +46218,17 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>5/15 02:00</t>
+          <t>5/14 02:00</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15T02:00+09:00</t>
+          <t>2026-05-14T02:00+09:00</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -27,7 +27,7 @@
     <sheet name="How_To_Read" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$C$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SB_Report'!$A$1:$C$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SB_Action_Detail'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Combo_Report_Index'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'New_Report_Index'!$A$1:$F$2</definedName>
@@ -39,7 +39,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Seasonal_Mode_Plan'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Mode_Plan_All'!$A$1:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Mission_DB'!$A$1:$S$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Condition_DB'!$A$1:$I$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Condition_DB'!$A$1:$I$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Conflict_Check'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Parse_Check'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Collected_URLs'!$A$1:$G$29</definedName>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -915,7 +915,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Any: 5경기 각 Finesse Goal 1회</t>
+          <t>4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -984,7 +984,7 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Any: 4경기 각 Cross Assist 1회</t>
+          <t>3-4-2-1 전술: 4경기 각 Cross Assist 1회</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>4-1-2-1-2 (2) 전술 사용</t>
+          <t>5-4-1 전술로 5승</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>3-4-2-1 전술 사용</t>
+          <t>Denmark 선수 1명 이상 선발하고 10경기 플레이</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Adapt Your Tactics (마감 5/22 02:00)</t>
+          <t>TOTS HM Hjulmand (마감 5/22 02:00)</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>5-4-1 전술로 5승</t>
+          <t>4경기 각각 1실점 이하</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Adapt Your Tactics (마감 5/22 02:00)</t>
+          <t>TOTS HM Hjulmand (마감 5/22 02:00)</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Denmark 선수 1명 이상 선발하고 10경기 플레이</t>
+          <t>Denmark 선수 2명 이상 선발하고 7승</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1196,12 +1196,12 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>4경기 각각 1실점 이하</t>
+          <t>라리가 선수 1명 이상 선발하고 2경기 플레이</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Hjulmand (마감 5/22 02:00)</t>
+          <t>Silver TOTS HM Trio (마감 5/22 02:00)</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Denmark 선수 2명 이상 선발하고 7승</t>
+          <t>TOTS 카드 1명 이상 선발하고 2승</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Hjulmand (마감 5/22 02:00)</t>
+          <t>Silver TOTS HM Trio (마감 5/22 02:00)</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>라리가 선수 1명 이상 선발하고 2경기 플레이</t>
+          <t>미국 선수 1명 이상 선발하고 2경기 플레이</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Trio (마감 5/22 02:00)</t>
+          <t>Silver TOTS HM Sarah Schupansky (마감 5/21 13:00)</t>
         </is>
       </c>
     </row>
@@ -1235,43 +1235,17 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>TOTS 카드 1명 이상 선발하고 2승</t>
+          <t>미국 선수 1명 이상 선발하고 2승</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Silver TOTS HM Trio (마감 5/22 02:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>미국 선수 1명 이상 선발하고 2경기 플레이</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
           <t>Silver TOTS HM Sarah Schupansky (마감 5/21 13:00)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>미국 선수 1명 이상 선발하고 2승</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Silver TOTS HM Sarah Schupansky (마감 5/21 13:00)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C53"/>
+  <autoFilter ref="A1:C51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2442,7 +2416,7 @@
           <t>LALIGA ST: Goal 10회
 Any: 5경기 각 Goal 1회
 Liga F: Goal 10회
-Any: 5경기 각 Finesse Goal 1회
+4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회
 Liga F: 2경기 각 Goal 1회
 NWSL: Goal 2회
 Any: 15경기 각 Finesse Goal 1회</t>
@@ -2452,7 +2426,7 @@
         <is>
           <t>Striker: Assist 4회
 Attacker: Assist 4회
-Any: 4경기 각 Cross Assist 1회
+3-4-2-1 전술: 4경기 각 Cross Assist 1회
 midfielder: Assist 4회
 Liga Portugal: 5경기 각 Assist 1회</t>
         </is>
@@ -2464,8 +2438,6 @@
 Spain 선수 1명 이상 선발하고 6경기 플레이
 4-4-2 전술로 5경기 플레이
 5-3-2 전술로 5경기 각각 1실점 이하
-4-1-2-1-2 (2) 전술 사용
-3-4-2-1 전술 사용
 5-4-1 전술로 5승
 Denmark 선수 1명 이상 선발하고 10경기 플레이
 4경기 각각 1실점 이하
@@ -12376,7 +12348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13607,12 +13579,12 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Formation</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>4-1-2-1-2 (2) 전술</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
@@ -13626,38 +13598,38 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Any: 5경기 각각 Finesse Goal 1회 이상</t>
+          <t>4-1-2-1-2 (2) 전술: 5경기 각각 Finesse Goal 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>O008-03</t>
+          <t>O008-04</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Other_Action</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
+          <t>Cross Assist</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
           <t>Formation</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Formation</t>
-        </is>
-      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>4-1-2-1-2 (2)</t>
+          <t>3-4-2-1 전술</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="8" t="inlineStr"/>
       <c r="H31" s="8" t="inlineStr">
@@ -13667,24 +13639,24 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>4-1-2-1-2 (2) 전술 사용</t>
+          <t>3-4-2-1 전술: 4경기 각각 Cross Assist 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>O008-04</t>
+          <t>O008-05</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Cross Assist</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -13698,24 +13670,24 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="8" t="inlineStr"/>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Any: 4경기 각각 Cross Assist 1회 이상</t>
+          <t>Win 5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>O008-04</t>
+          <t>O008-05</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -13735,52 +13707,52 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>3-4-2-1</t>
+          <t>5-4-1</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="8" t="inlineStr"/>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>3-4-2-1 전술 사용</t>
+          <t>5-4-1 전술로 5승</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>O008-05</t>
+          <t>O009-01</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
       <c r="H34" s="8" t="inlineStr">
@@ -13790,38 +13762,38 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Win 5</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>O008-05</t>
+          <t>O009-01</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Other_Action</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Formation</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Formation</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>5-4-1</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G35" s="8" t="inlineStr"/>
       <c r="H35" s="8" t="inlineStr">
@@ -13831,24 +13803,24 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>5-4-1 전술로 5승</t>
+          <t>Play 10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>O009-01</t>
+          <t>O009-02</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -13858,11 +13830,11 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>midfielder</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
       <c r="H36" s="8" t="inlineStr">
@@ -13872,38 +13844,38 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>midfielder: Assist 4회</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>O009-01</t>
+          <t>O009-03</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>League</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Liga Portugal</t>
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G37" s="8" t="inlineStr"/>
       <c r="H37" s="8" t="inlineStr">
@@ -13913,34 +13885,34 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>O009-02</t>
+          <t>O009-03</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Other_Action</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Concede Limit</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>midfielder</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
@@ -13949,19 +13921,19 @@
       <c r="G38" s="8" t="inlineStr"/>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>midfielder: Assist 4회</t>
+          <t>4경기 각각 1실점 이하</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>O009-03</t>
+          <t>O009-04</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -13976,16 +13948,16 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>League</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Liga Portugal</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr">
@@ -14002,17 +13974,17 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>O009-03</t>
+          <t>O009-04</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Other_Action</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Concede Limit</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -14026,89 +13998,89 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G40" s="8" t="inlineStr"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>4경기 각각 1실점 이하</t>
+          <t>Win 7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>O009-04</t>
+          <t>O009-05</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>League</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Liga Portugal</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G41" s="8" t="inlineStr"/>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Liga Portugal: 5경기 각각 Assist 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>O009-04</t>
+          <t>O010-01</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>League</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>LALIGA</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="inlineStr"/>
       <c r="H42" s="8" t="inlineStr">
@@ -14118,65 +14090,65 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>Win 7</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>O009-05</t>
+          <t>O010-01</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>League</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Liga Portugal</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G43" s="8" t="inlineStr"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>Liga Portugal: 5경기 각각 Assist 1회 이상</t>
+          <t>Play 2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>O010-01</t>
+          <t>O010-02</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -14186,52 +14158,52 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>LALIGA</t>
+          <t>Liga F</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="8" t="inlineStr"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Liga F: 2경기 각각 Goal 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>O010-01</t>
+          <t>O010-03</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Rarity/Competition</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>TOTS</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr"/>
       <c r="H45" s="8" t="inlineStr">
@@ -14241,34 +14213,34 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>O010-02</t>
+          <t>O010-03</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>League</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Liga F</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
@@ -14277,43 +14249,43 @@
       <c r="G46" s="8" t="inlineStr"/>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Liga F: 2경기 각각 Goal 1회 이상</t>
+          <t>Win 2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>O010-03</t>
+          <t>O011-01</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Rarity/Competition</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>TOTS</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G47" s="8" t="inlineStr"/>
       <c r="H47" s="8" t="inlineStr">
@@ -14323,14 +14295,14 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Play 10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>O010-03</t>
+          <t>O011-02</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -14354,7 +14326,7 @@
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G48" s="8" t="inlineStr"/>
       <c r="H48" s="8" t="inlineStr">
@@ -14364,24 +14336,24 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>Win 5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>O011-01</t>
+          <t>O011-03</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -14400,19 +14372,19 @@
       <c r="G49" s="8" t="inlineStr"/>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Any: 10경기 각각 Goal 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>O011-02</t>
+          <t>O011-04</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -14436,7 +14408,7 @@
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G50" s="8" t="inlineStr"/>
       <c r="H50" s="8" t="inlineStr">
@@ -14446,14 +14418,14 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Win 5</t>
+          <t>Win 8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>O011-03</t>
+          <t>O011-05</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -14463,7 +14435,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Assist</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -14487,24 +14459,24 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Any: 10경기 각각 Goal 1회 이상</t>
+          <t>Any: 10경기 각각 Assist 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>O011-04</t>
+          <t>O012-01</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -14518,7 +14490,7 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr">
@@ -14528,14 +14500,14 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Win 8</t>
+          <t>Play 3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>O011-05</t>
+          <t>O012-02</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -14545,7 +14517,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -14559,34 +14531,34 @@
         </is>
       </c>
       <c r="F53" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Any: 10경기 각각 Assist 1회 이상</t>
+          <t>Any: Goal 3회</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>O012-01</t>
+          <t>O012-03</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -14610,24 +14582,24 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>Play 3</t>
+          <t>Win 3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>O012-02</t>
+          <t>O013-01</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -14641,7 +14613,7 @@
         </is>
       </c>
       <c r="F55" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G55" s="8" t="inlineStr"/>
       <c r="H55" s="8" t="inlineStr">
@@ -14651,14 +14623,14 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Any: Goal 3회</t>
+          <t>Play 10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>O012-03</t>
+          <t>O013-02</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -14682,7 +14654,7 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G56" s="8" t="inlineStr"/>
       <c r="H56" s="8" t="inlineStr">
@@ -14692,34 +14664,34 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Win 10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>O013-01</t>
+          <t>O013-03</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
@@ -14733,24 +14705,24 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Dutch: Goal 10회</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>O013-02</t>
+          <t>O014-01</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -14764,7 +14736,7 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8" t="inlineStr"/>
       <c r="H58" s="8" t="inlineStr">
@@ -14774,14 +14746,14 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Play 3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>O013-03</t>
+          <t>O014-02</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -14796,16 +14768,16 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F59" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G59" s="8" t="inlineStr"/>
       <c r="H59" s="8" t="inlineStr">
@@ -14815,24 +14787,24 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Dutch: Goal 10회</t>
+          <t>Any: Goal 3회</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>O014-01</t>
+          <t>O014-03</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -14856,14 +14828,14 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Play 3</t>
+          <t>Win 3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>O014-02</t>
+          <t>O015-01</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -14887,7 +14859,7 @@
         </is>
       </c>
       <c r="F61" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr">
@@ -14897,24 +14869,24 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Any: Goal 3회</t>
+          <t>Any: Goal 2회</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>O014-03</t>
+          <t>O015-02</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -14928,7 +14900,7 @@
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr">
@@ -14938,24 +14910,24 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Any: Goal 2회</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>O015-01</t>
+          <t>O016-01</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -14969,7 +14941,7 @@
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
       <c r="H63" s="8" t="inlineStr">
@@ -14979,14 +14951,14 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Any: Goal 2회</t>
+          <t>Play 3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>O015-02</t>
+          <t>O016-02</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -15010,7 +14982,7 @@
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr">
@@ -15020,24 +14992,24 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Any: Goal 2회</t>
+          <t>Any: Goal 3회</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>O016-01</t>
+          <t>O016-03</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -15061,38 +15033,38 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Play 3</t>
+          <t>Win 3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>O016-02</t>
+          <t>O017-01</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Nation</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" s="8" t="inlineStr"/>
       <c r="H66" s="8" t="inlineStr">
@@ -15102,24 +15074,24 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>Any: Goal 3회</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>O016-03</t>
+          <t>O017-01</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -15133,7 +15105,7 @@
         </is>
       </c>
       <c r="F67" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" s="8" t="inlineStr"/>
       <c r="H67" s="8" t="inlineStr">
@@ -15143,38 +15115,38 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Play 2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>O017-01</t>
+          <t>O017-02</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nation</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>NWSL</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" s="8" t="inlineStr"/>
       <c r="H68" s="8" t="inlineStr">
@@ -15184,38 +15156,38 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>NWSL: Goal 2회</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>O017-01</t>
+          <t>O017-03</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Nation</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
       <c r="H69" s="8" t="inlineStr">
@@ -15225,34 +15197,34 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>O017-02</t>
+          <t>O017-03</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>NWSL</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
@@ -15266,38 +15238,38 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>NWSL: Goal 2회</t>
+          <t>Win 2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>O017-03</t>
+          <t>O018-01</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Nation</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F71" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr">
@@ -15307,24 +15279,24 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Play 5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>O017-03</t>
+          <t>O018-02</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -15338,7 +15310,7 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr">
@@ -15348,14 +15320,14 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>Play 10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>O018-01</t>
+          <t>O018-03</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -15379,7 +15351,7 @@
         </is>
       </c>
       <c r="F73" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
       <c r="H73" s="8" t="inlineStr">
@@ -15389,14 +15361,14 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>O018-02</t>
+          <t>O018-04</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -15420,7 +15392,7 @@
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G74" s="8" t="inlineStr"/>
       <c r="H74" s="8" t="inlineStr">
@@ -15430,14 +15402,14 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>O018-03</t>
+          <t>O018-05</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -15461,7 +15433,7 @@
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr">
@@ -15471,14 +15443,14 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Play 25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>O018-04</t>
+          <t>O019-01</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
@@ -15502,7 +15474,7 @@
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G76" s="8" t="inlineStr"/>
       <c r="H76" s="8" t="inlineStr">
@@ -15512,14 +15484,14 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>Play 20</t>
+          <t>Play 5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>O018-05</t>
+          <t>O019-02</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -15543,7 +15515,7 @@
         </is>
       </c>
       <c r="F77" s="8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
       <c r="H77" s="8" t="inlineStr">
@@ -15553,14 +15525,14 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>Play 25</t>
+          <t>Play 5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>O019-01</t>
+          <t>O019-03</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -15601,7 +15573,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>O019-02</t>
+          <t>O019-04</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -15642,7 +15614,7 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>O019-03</t>
+          <t>O019-05</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -15683,7 +15655,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>O019-04</t>
+          <t>O019-06</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -15724,7 +15696,7 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>O019-05</t>
+          <t>O019-07</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -15765,7 +15737,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>O019-06</t>
+          <t>O019-08</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -15806,7 +15778,7 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>O019-07</t>
+          <t>O019-09</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -15847,7 +15819,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>O019-08</t>
+          <t>O019-10</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -15888,7 +15860,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>O019-09</t>
+          <t>O021-01</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -15929,7 +15901,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>O019-10</t>
+          <t>O021-02</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -15970,7 +15942,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>O021-01</t>
+          <t>O021-03</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -16011,7 +15983,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>O021-02</t>
+          <t>O021-04</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -16052,7 +16024,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>O021-03</t>
+          <t>O021-05</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -16093,7 +16065,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>O021-04</t>
+          <t>O021-06</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -16134,7 +16106,7 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>O021-05</t>
+          <t>O021-07</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -16175,7 +16147,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>O021-06</t>
+          <t>O021-08</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -16216,7 +16188,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>O021-07</t>
+          <t>O022-01</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -16240,7 +16212,7 @@
         </is>
       </c>
       <c r="F94" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G94" s="8" t="inlineStr"/>
       <c r="H94" s="8" t="inlineStr">
@@ -16250,24 +16222,24 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Play 3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>O021-08</t>
+          <t>O022-02</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -16281,34 +16253,34 @@
         </is>
       </c>
       <c r="F95" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Any: 3경기 각각 Goal 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>O022-01</t>
+          <t>O022-03</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -16332,65 +16304,65 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>Play 3</t>
+          <t>Any: Goal 3회</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>O022-02</t>
+          <t>O023-01</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Nation</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F97" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>Any: 3경기 각각 Goal 1회 이상</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>O022-03</t>
+          <t>O023-01</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -16404,7 +16376,7 @@
         </is>
       </c>
       <c r="F98" s="8" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G98" s="8" t="inlineStr"/>
       <c r="H98" s="8" t="inlineStr">
@@ -16414,14 +16386,14 @@
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>Any: Goal 3회</t>
+          <t>Play 40</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>O023-01</t>
+          <t>O023-02</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -16462,17 +16434,17 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>O023-01</t>
+          <t>O023-02</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
@@ -16486,7 +16458,7 @@
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G100" s="8" t="inlineStr"/>
       <c r="H100" s="8" t="inlineStr">
@@ -16496,14 +16468,14 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>Play 40</t>
+          <t>Win 20</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>O023-02</t>
+          <t>O024-01</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -16527,7 +16499,7 @@
         </is>
       </c>
       <c r="F101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G101" s="8" t="inlineStr"/>
       <c r="H101" s="8" t="inlineStr">
@@ -16544,17 +16516,17 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>O023-02</t>
+          <t>O024-01</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Other_Action</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Concede Limit</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
@@ -16573,43 +16545,43 @@
       <c r="G102" s="8" t="inlineStr"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>Win 20</t>
+          <t>20경기 각각 1실점 이하</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>O024-01</t>
+          <t>O024-02</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Nation</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F103" s="8" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
       <c r="H103" s="8" t="inlineStr">
@@ -16619,24 +16591,24 @@
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Win 30</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>O024-01</t>
+          <t>O025-01</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Other_Action</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Concede Limit</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -16650,34 +16622,34 @@
         </is>
       </c>
       <c r="F104" s="8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G104" s="8" t="inlineStr"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>20경기 각각 1실점 이하</t>
+          <t>Play 1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>O024-02</t>
+          <t>O025-02</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -16691,7 +16663,7 @@
         </is>
       </c>
       <c r="F105" s="8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
       <c r="H105" s="8" t="inlineStr">
@@ -16701,14 +16673,14 @@
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>Win 30</t>
+          <t>Play 2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>O025-01</t>
+          <t>O025-03</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -16732,7 +16704,7 @@
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" s="8" t="inlineStr"/>
       <c r="H106" s="8" t="inlineStr">
@@ -16742,14 +16714,14 @@
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Play 3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>O025-02</t>
+          <t>O025-04</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -16773,7 +16745,7 @@
         </is>
       </c>
       <c r="F107" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
       <c r="H107" s="8" t="inlineStr">
@@ -16783,14 +16755,14 @@
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Play 4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>O025-03</t>
+          <t>O025-05</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
@@ -16814,7 +16786,7 @@
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G108" s="8" t="inlineStr"/>
       <c r="H108" s="8" t="inlineStr">
@@ -16824,14 +16796,14 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>Play 3</t>
+          <t>Play 5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>O025-04</t>
+          <t>O025-06</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -16855,7 +16827,7 @@
         </is>
       </c>
       <c r="F109" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
       <c r="H109" s="8" t="inlineStr">
@@ -16865,38 +16837,38 @@
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>Play 4</t>
+          <t>Play 6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>O025-05</t>
+          <t>O026-01</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G110" s="8" t="inlineStr"/>
       <c r="H110" s="8" t="inlineStr">
@@ -16906,24 +16878,24 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>O025-06</t>
+          <t>O026-01</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Finesse Goal</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
@@ -16937,24 +16909,24 @@
         </is>
       </c>
       <c r="F111" s="8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>Play 6</t>
+          <t>Any: 15경기 각각 Finesse Goal 1회 이상</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>O026-01</t>
+          <t>O026-02</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -16995,17 +16967,17 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>O026-01</t>
+          <t>O026-02</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Performer</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Finesse Goal</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -17019,48 +16991,48 @@
         </is>
       </c>
       <c r="F113" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G113" s="8" t="inlineStr"/>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Any: 15경기 각각 Finesse Goal 1회 이상</t>
+          <t>Win 25</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>O026-02</t>
+          <t>O027-01</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Clean Sheet</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G114" s="8" t="inlineStr"/>
       <c r="H114" s="8" t="inlineStr">
@@ -17070,38 +17042,38 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Clean Sheet 20</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>O026-02</t>
+          <t>O027-02</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Match_Result</t>
+          <t>Squad</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Starting XI</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Nation</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F115" s="8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
       <c r="H115" s="8" t="inlineStr">
@@ -17111,14 +17083,14 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Win 25</t>
+          <t>선발에 포함</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>O027-01</t>
+          <t>O027-02</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -17128,7 +17100,7 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Clean Sheet</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -17142,7 +17114,7 @@
         </is>
       </c>
       <c r="F116" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G116" s="8" t="inlineStr"/>
       <c r="H116" s="8" t="inlineStr">
@@ -17152,38 +17124,38 @@
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>Clean Sheet 20</t>
+          <t>Win 35</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>O027-02</t>
+          <t>O028-01</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Squad</t>
+          <t>Match_Count</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Starting XI</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Nation</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F117" s="8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
       <c r="H117" s="8" t="inlineStr">
@@ -17193,14 +17165,14 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>선발에 포함</t>
+          <t>Play 30</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>O027-02</t>
+          <t>O028-02</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -17224,7 +17196,7 @@
         </is>
       </c>
       <c r="F118" s="8" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G118" s="8" t="inlineStr"/>
       <c r="H118" s="8" t="inlineStr">
@@ -17234,24 +17206,24 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>Win 35</t>
+          <t>Win 10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>O028-01</t>
+          <t>O028-03</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Match_Count</t>
+          <t>Match_Result</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -17265,7 +17237,7 @@
         </is>
       </c>
       <c r="F119" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
       <c r="H119" s="8" t="inlineStr">
@@ -17275,14 +17247,14 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Play 30</t>
+          <t>Win 20</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>O028-02</t>
+          <t>O028-04</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
@@ -17306,7 +17278,7 @@
         </is>
       </c>
       <c r="F120" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G120" s="8" t="inlineStr"/>
       <c r="H120" s="8" t="inlineStr">
@@ -17316,14 +17288,14 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Win 30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>O028-03</t>
+          <t>O028-05</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -17347,7 +17319,7 @@
         </is>
       </c>
       <c r="F121" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
       <c r="H121" s="8" t="inlineStr">
@@ -17357,94 +17329,12 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>Win 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>O028-04</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>Match_Result</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G122" s="8" t="inlineStr"/>
-      <c r="H122" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>Win 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>O028-05</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Match_Result</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="F123" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I123" s="8" t="inlineStr">
-        <is>
           <t>Win 40</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I123"/>
+  <autoFilter ref="A1:I121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17737,7 +17627,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Finesse Goal, Formation</t>
+          <t>Finesse Goal</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -20339,7 +20229,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Any: 5경기 각 Finesse Goal 1회</t>
+          <t>4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -20349,7 +20239,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>4-1-2-1-2 (2) 전술 사용</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -20415,12 +20305,12 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Any: 4경기 각 Cross Assist 1회</t>
+          <t>3-4-2-1 전술: 4경기 각 Cross Assist 1회</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>3-4-2-1 전술 사용</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -24127,7 +24017,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Any: 5경기 각 Finesse Goal 1회</t>
+          <t>4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -24137,7 +24027,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>4-1-2-1-2 (2) 전술 사용</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -24233,12 +24123,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Any: 4경기 각 Cross Assist 1회</t>
+          <t>3-4-2-1 전술: 4경기 각 Cross Assist 1회</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>3-4-2-1 전술 사용</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -28105,7 +27995,7 @@
           <t>LALIGA ST: Goal 10회
 Any: 5경기 각 Goal 1회
 Liga F: Goal 10회
-Any: 5경기 각 Finesse Goal 1회
+4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회
 Liga F: 2경기 각 Goal 1회
 NWSL: Goal 2회</t>
         </is>
@@ -28114,7 +28004,7 @@
         <is>
           <t>Striker: Assist 4회
 Attacker: Assist 4회
-Any: 4경기 각 Cross Assist 1회
+3-4-2-1 전술: 4경기 각 Cross Assist 1회
 midfielder: Assist 4회
 Liga Portugal: 5경기 각 Assist 1회</t>
         </is>
@@ -28126,8 +28016,6 @@
 Spain 선수 1명 이상 선발하고 6경기 플레이
 4-4-2 전술로 5경기 플레이
 5-3-2 전술로 5경기 각각 1실점 이하
-4-1-2-1-2 (2) 전술 사용
-3-4-2-1 전술 사용
 5-4-1 전술로 5승
 Denmark 선수 1명 이상 선발하고 10경기 플레이
 4경기 각각 1실점 이하
@@ -28740,7 +28628,7 @@
           <t>LALIGA ST: Goal 10회
 Any: 5경기 각 Goal 1회
 Liga F: Goal 10회
-Any: 5경기 각 Finesse Goal 1회
+4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회
 Liga F: 2경기 각 Goal 1회
 NWSL: Goal 2회</t>
         </is>
@@ -28749,7 +28637,7 @@
         <is>
           <t>Striker: Assist 4회
 Attacker: Assist 4회
-Any: 4경기 각 Cross Assist 1회
+3-4-2-1 전술: 4경기 각 Cross Assist 1회
 midfielder: Assist 4회
 Liga Portugal: 5경기 각 Assist 1회</t>
         </is>
@@ -28761,8 +28649,6 @@
 Spain 선수 1명 이상 선발하고 6경기 플레이
 4-4-2 전술로 5경기 플레이
 5-3-2 전술로 5경기 각각 1실점 이하
-4-1-2-1-2 (2) 전술 사용
-3-4-2-1 전술 사용
 5-4-1 전술로 5승
 Denmark 선수 1명 이상 선발하고 10경기 플레이
 4경기 각각 1실점 이하
@@ -36343,7 +36229,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Any: 5경기 각 Finesse Goal 1회</t>
+          <t>4-1-2-1-2 (2) 전술: 5경기 각 Finesse Goal 1회</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -36353,7 +36239,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>4-1-2-1-2 (2) 전술 사용</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -36449,12 +36335,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Any: 4경기 각 Cross Assist 1회</t>
+          <t>3-4-2-1 전술: 4경기 각 Cross Assist 1회</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>3-4-2-1 전술 사용</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">

--- a/latest/objectives_latest.xlsx
+++ b/latest/objectives_latest.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>20경기</t>
+          <t>25경기</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -784,7 +784,7 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Any: Power Shot Goal 30회</t>
+          <t>Any: 3경기 각 Header Goal 1회</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -797,12 +797,12 @@
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>LALIGA ST: Goal 10회</t>
+          <t>Any: Power Shot Goal 30회</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>TOTS HM Borja Iglesias (마감 5/27 02:00)</t>
+          <t>Curtain Call (마감 6/5 02:00)</t>
         </is>
       </c>
     </row>
@@ -810,59 +810,55 @@
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>LALIGA ST: Goal 10회</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>TOTS HM Borja Iglesias (마감 5/27 02:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>Any: 5경기 각 Goal 1회</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>TOTS HM Borja Iglesias (마감 5/27 02:00)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>To do (어시스트)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>4-1-4-1 전술: Assist 10회</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Get in the Game (마감 6/8 02:00)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Striker: Assist 4회</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>TOTS HM Borja Iglesias (마감 5/27 02:00)</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>To do (기타)</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>3-5-2 전술로 5경기 플레이</t>
+          <t>Any: 25경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Get in the Game (마감 6/8 02:00)</t>
+          <t>Curtain Call (마감 6/5 02:00)</t>
         </is>
       </c>
     </row>
@@ -870,20 +866,24 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>3-4-3 전술로 클린시트 4회</t>
+          <t>Striker: Assist 4회</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Get in the Game (마감 6/8 02:00)</t>
+          <t>TOTS HM Borja Iglesias (마감 5/27 02:00)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>To do (기타)</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>5-2-1-2 전술로 8경기 각각 1실점 이하</t>
+          <t>3-5-2 전술로 5경기 플레이</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -896,12 +896,12 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Arsenal (Premier League) 선수 1명 이상 선발하고 2경기 플레이</t>
+          <t>3-4-3 전술로 클린시트 4회</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Final in Budapest (마감 5/30 02:00)</t>
+          <t>Get in the Game (마감 6/8 02:00)</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>PSG (Ligue 1) 선수 1명 이상 선발하고 2경기 플레이</t>
+          <t>5-2-1-2 전술로 8경기 각각 1실점 이하</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Final in Budapest (마감 5/30 02:00)</t>
+          <t>Get in the Game (마감 6/8 02:00)</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>Arsenal (Premier League) 선수 1명 이상 선발하고 2경기 플레이</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Curtain Call (마감 6/5 02:00)</t>
+          <t>Final in Budapest (마감 5/30 02:00)</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>PSG (Ligue 1) 선수 1명 이상 선발하고 2경기 플레이</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Curtain Call (마감 6/5 02:00)</t>
+          <t>Final in Budapest (마감 5/30 02:00)</t>
         </is>
       </c>
     </row>
@@ -2088,6 +2088,7 @@
         <is>
           <t>4-2-2-2 전술: 5경기 각 Finesse Goal 1회
 Any: Finesse Goal 30회
+Any: 3경기 각 Header Goal 1회
 Any: Power Shot Goal 30회
 Any: Goal 5회
 LALIGA ST: Goal 10회
@@ -2098,6 +2099,7 @@
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>4-1-4-1 전술: Assist 10회
+Any: 25경기 각 Through Ball Assist 1회
 Any: Assist 5회
 Striker: Assist 4회</t>
         </is>
@@ -2107,8 +2109,6 @@
           <t>3-5-2 전술로 5경기 플레이
 3-4-3 전술로 클린시트 4회
 5-2-1-2 전술로 8경기 각각 1실점 이하
-원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).
-원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).
 20경기 각각 1실점 이하
 클린시트 10회
 10승
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -6793,11 +6793,11 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Through Ball Assist</t>
         </is>
       </c>
       <c r="L52" s="8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
@@ -6880,11 +6880,11 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Header Goal</t>
         </is>
       </c>
       <c r="L53" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
@@ -15808,26 +15808,26 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Other_Action</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Through Ball Assist</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>Any: 25경기 각각 Through Ball Assist 1회 이상</t>
         </is>
       </c>
     </row>
@@ -15849,26 +15849,26 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Other_Action</t>
+          <t>Performer</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Header Goal</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F61" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>Any: 3경기 각각 Header Goal 1회 이상</t>
         </is>
       </c>
     </row>
@@ -18929,12 +18929,12 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Through Ball Assist</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Header Goal</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>TOTS: Champions Qualification Points Compete in Live Events to earn Champions Qualification Points! 100 Points Expires in 1 day 3 Objectives 67% 33%</t>
+          <t>TOTS: Champions Qualification Points Compete in Live Events to earn Champions Qualification Points! 100 Points Expires in 24 hours 3 Objectives 67% 33%</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TOTS: Champions Objective Compete in Champions to earn packs, Evolutions, and a Ultimate TOTS Guarantee Pack! All rewards are untradeable. Ultimate Men/Women Tots Player Pack Expires in 1 day 1,500 total 5 Objectives 78% 22%</t>
+          <t>TOTS: Champions Objective Compete in Champions to earn packs, Evolutions, and a Ultimate TOTS Guarantee Pack! All rewards are untradeable. Ultimate Men/Women Tots Player Pack Expires in 24 hours 1,500 total 5 Objectives 78% 22%</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -21269,12 +21269,12 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Any: 25경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -21283,7 +21283,7 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Any: 3경기 각 Header Goal 1회</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -21354,7 +21354,7 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -27136,12 +27136,12 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Any: 25경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -27150,7 +27150,7 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Any: 3경기 각 Header Goal 1회</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -27238,7 +27238,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -27247,7 +27247,7 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -31223,6 +31223,7 @@
         <is>
           <t>4-2-2-2 전술: 5경기 각 Finesse Goal 1회
 Any: Finesse Goal 30회
+Any: 3경기 각 Header Goal 1회
 Any: Power Shot Goal 30회
 LALIGA ST: Goal 10회
 Any: 5경기 각 Goal 1회</t>
@@ -31231,6 +31232,7 @@
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>4-1-4-1 전술: Assist 10회
+Any: 25경기 각 Through Ball Assist 1회
 Striker: Assist 4회</t>
         </is>
       </c>
@@ -31239,8 +31241,6 @@
           <t>3-5-2 전술로 5경기 플레이
 3-4-3 전술로 클린시트 4회
 5-2-1-2 전술로 8경기 각각 1실점 이하
-원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).
-원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).
 20경기 각각 1실점 이하
 클린시트 10회
 Spain 선수 2명 이상 선발하고 6승
@@ -31856,7 +31856,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -31874,6 +31874,7 @@
         <is>
           <t>4-2-2-2 전술: 5경기 각 Finesse Goal 1회
 Any: Finesse Goal 30회
+Any: 3경기 각 Header Goal 1회
 Any: Power Shot Goal 30회
 LALIGA ST: Goal 10회
 Any: 5경기 각 Goal 1회</t>
@@ -31882,6 +31883,7 @@
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>4-1-4-1 전술: Assist 10회
+Any: 25경기 각 Through Ball Assist 1회
 Striker: Assist 4회</t>
         </is>
       </c>
@@ -31890,8 +31892,6 @@
           <t>3-5-2 전술로 5경기 플레이
 3-4-3 전술로 클린시트 4회
 5-2-1-2 전술로 8경기 각각 1실점 이하
-원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).
-원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).
 20경기 각각 1실점 이하
 클린시트 10회
 Spain 선수 2명 이상 선발하고 6승
@@ -39540,7 +39540,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -39633,7 +39633,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -39726,7 +39726,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -40212,7 +40212,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -40309,7 +40309,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -40600,7 +40600,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 1 day</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -40829,12 +40829,12 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Any: 25경기 각 Through Ball Assist 1회</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Assist with a through ball in 25 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -40843,7 +40843,7 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Any: 3경기 각 Header Goal 1회</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>원문 확인: Score with a header in 3 separate matches in Squad Battles on min. Semi-Pro difficulty (or Rivals/Champions/Live Events).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -40940,7 +40940,7 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
